--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T08:44:28+00:00</t>
+    <t>2026-09-17T13:01:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -949,7 +949,7 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActEncounterCode-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActEncounterCode-cisis|20260716085852</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:01:59+00:00</t>
+    <t>2026-09-22T12:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="617">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T12:10:06+00:00</t>
+    <t>2026-09-22T12:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -959,6 +959,127 @@
   </si>
   <si>
     <t>PV1-2</t>
+  </si>
+  <si>
+    <t>Encounter.class.id</t>
+  </si>
+  <si>
+    <t>Encounter.class.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Encounter.class.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Encounter.class.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Encounter.class.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Encounter.class.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
   </si>
   <si>
     <t>Encounter.classHistory</t>
@@ -2110,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN100"/>
+  <dimension ref="A1:AN107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.34765625" customWidth="true" bestFit="true"/>
@@ -6380,7 +6501,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6392,13 +6513,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>281</v>
+        <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>305</v>
+        <v>104</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>306</v>
+        <v>105</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6449,19 +6570,19 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>304</v>
+        <v>106</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6478,21 +6599,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6504,15 +6625,17 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6549,31 +6672,31 @@
         <v>81</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6590,21 +6713,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6613,21 +6736,23 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>111</v>
+        <v>307</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6675,75 +6800,73 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>117</v>
+        <v>311</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>107</v>
+        <v>312</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6791,39 +6914,39 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6843,19 +6966,21 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6879,13 +7004,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>313</v>
+        <v>81</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -6903,10 +7028,10 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -6921,21 +7046,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>107</v>
+        <v>326</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6943,7 +7068,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6955,19 +7080,21 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7015,10 +7142,10 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>89</v>
@@ -7033,21 +7160,21 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>107</v>
+        <v>333</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7058,7 +7185,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
@@ -7070,18 +7197,20 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>230</v>
+        <v>336</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7105,11 +7234,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>322</v>
+        <v>81</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7127,13 +7258,13 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
@@ -7142,24 +7273,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>325</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7170,7 +7301,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7179,16 +7310,16 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7215,13 +7346,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>330</v>
+        <v>81</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7239,13 +7370,13 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
@@ -7254,7 +7385,7 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>107</v>
@@ -7263,15 +7394,15 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7294,13 +7425,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>230</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>333</v>
+        <v>104</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>334</v>
+        <v>105</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7327,13 +7458,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7351,7 +7482,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7363,38 +7494,38 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>336</v>
+        <v>107</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>338</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>340</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7403,19 +7534,19 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>341</v>
+        <v>110</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>342</v>
+        <v>111</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>343</v>
+        <v>112</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>344</v>
+        <v>113</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7465,31 +7596,31 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>339</v>
+        <v>117</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>345</v>
+        <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>346</v>
+        <v>107</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
@@ -7501,7 +7632,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7514,22 +7645,26 @@
         <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>350</v>
+        <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>351</v>
+        <v>289</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7577,7 +7712,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>349</v>
+        <v>291</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7589,38 +7724,38 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>355</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7632,13 +7767,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>358</v>
+        <v>148</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7665,13 +7800,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7689,13 +7824,13 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
@@ -7704,10 +7839,10 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>362</v>
+        <v>107</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -7718,10 +7853,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7729,10 +7864,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7741,16 +7876,16 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7801,13 +7936,13 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
@@ -7816,24 +7951,24 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>367</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>368</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7844,7 +7979,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -7853,18 +7988,20 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>104</v>
+        <v>359</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -7889,13 +8026,11 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -7913,50 +8048,50 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>106</v>
+        <v>358</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>107</v>
+        <v>364</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -7965,20 +8100,18 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>111</v>
+        <v>367</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8003,13 +8136,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>81</v>
+        <v>369</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8027,22 +8160,22 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>117</v>
+        <v>366</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>107</v>
@@ -8051,51 +8184,47 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>81</v>
+        <v>371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>289</v>
+        <v>373</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8119,13 +8248,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8143,50 +8272,50 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>291</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>193</v>
+        <v>376</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8198,16 +8327,16 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8233,13 +8362,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8257,13 +8386,13 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
@@ -8272,24 +8401,24 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8300,7 +8429,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8309,16 +8438,16 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>256</v>
+        <v>390</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8369,13 +8498,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8384,35 +8513,35 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>383</v>
+        <v>107</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>81</v>
+        <v>397</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8421,16 +8550,16 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8481,13 +8610,13 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
@@ -8496,24 +8625,24 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>391</v>
+        <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8536,13 +8665,13 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>394</v>
+        <v>281</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8593,7 +8722,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8608,24 +8737,24 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8648,17 +8777,15 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>400</v>
+        <v>104</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8707,7 +8834,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>399</v>
+        <v>106</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8719,38 +8846,38 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>404</v>
+        <v>107</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -8762,16 +8889,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>408</v>
+        <v>110</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>409</v>
+        <v>111</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>410</v>
+        <v>112</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>411</v>
+        <v>113</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8821,43 +8948,43 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>407</v>
+        <v>117</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>412</v>
+        <v>107</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8870,24 +8997,26 @@
         <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>416</v>
+        <v>289</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>417</v>
+        <v>290</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -8911,13 +9040,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8935,7 +9064,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>414</v>
+        <v>291</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8947,31 +9076,31 @@
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>422</v>
+        <v>193</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8990,16 +9119,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>426</v>
+        <v>230</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9025,13 +9154,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9049,7 +9178,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9064,24 +9193,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9092,7 +9221,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9101,16 +9230,16 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9161,13 +9290,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9179,21 +9308,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9213,16 +9342,16 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>103</v>
+        <v>426</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>104</v>
+        <v>427</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>105</v>
+        <v>428</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9273,7 +9402,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>106</v>
+        <v>425</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9285,19 +9414,19 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>107</v>
+        <v>430</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64">
@@ -9309,7 +9438,7 @@
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9325,20 +9454,18 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>110</v>
+        <v>434</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>111</v>
+        <v>435</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9387,7 +9514,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>117</v>
+        <v>433</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9399,63 +9526,61 @@
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>107</v>
+        <v>437</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>110</v>
+        <v>256</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>289</v>
+        <v>440</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>290</v>
+        <v>441</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
       </c>
@@ -9503,47 +9628,47 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>291</v>
+        <v>439</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>193</v>
+        <v>444</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>81</v>
+        <v>446</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
@@ -9555,19 +9680,19 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9617,10 +9742,10 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>89</v>
@@ -9632,35 +9757,35 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>81</v>
+        <v>455</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>81</v>
@@ -9669,18 +9794,20 @@
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>230</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -9708,10 +9835,10 @@
         <v>174</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9729,13 +9856,13 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
@@ -9744,35 +9871,35 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>107</v>
+        <v>462</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>81</v>
+        <v>455</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -9781,18 +9908,20 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -9841,13 +9970,13 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
@@ -9856,24 +9985,24 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9884,7 +10013,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -9893,20 +10022,18 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>454</v>
+        <v>281</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9955,7 +10082,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9973,7 +10100,7 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -9984,10 +10111,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10010,17 +10137,15 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>281</v>
+        <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>460</v>
+        <v>104</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10069,7 +10194,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>106</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10081,13 +10206,13 @@
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>463</v>
+        <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -10098,21 +10223,21 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
@@ -10124,15 +10249,17 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10181,19 +10308,19 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -10210,14 +10337,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10230,24 +10357,26 @@
         <v>81</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>111</v>
+        <v>289</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>112</v>
+        <v>290</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
       </c>
@@ -10295,7 +10424,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>117</v>
+        <v>291</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10313,7 +10442,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -10324,46 +10453,44 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>288</v>
+        <v>476</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>110</v>
+        <v>477</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>289</v>
+        <v>478</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>290</v>
+        <v>479</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10411,39 +10538,39 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>291</v>
+        <v>475</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>193</v>
+        <v>481</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>81</v>
+        <v>482</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10466,13 +10593,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10499,13 +10626,13 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>81</v>
+        <v>487</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -10523,7 +10650,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10541,21 +10668,21 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>470</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10578,13 +10705,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>103</v>
+        <v>489</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>104</v>
+        <v>490</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>105</v>
+        <v>491</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10635,7 +10762,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>106</v>
+        <v>488</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10647,13 +10774,13 @@
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>107</v>
+        <v>492</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -10664,21 +10791,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
@@ -10690,16 +10817,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>494</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>111</v>
+        <v>495</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>112</v>
+        <v>496</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>113</v>
+        <v>497</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10737,19 +10864,19 @@
         <v>81</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>117</v>
+        <v>493</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10761,13 +10888,13 @@
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>107</v>
+        <v>498</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -10778,10 +10905,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10798,26 +10925,24 @@
         <v>81</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>170</v>
+        <v>281</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>221</v>
+        <v>501</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -10841,13 +10966,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -10865,7 +10990,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>227</v>
+        <v>499</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10883,21 +11008,21 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>228</v>
+        <v>503</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10905,7 +11030,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -10917,23 +11042,19 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>230</v>
+        <v>103</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>231</v>
+        <v>104</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
       </c>
@@ -10957,11 +11078,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -10979,7 +11102,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10991,38 +11114,38 @@
         <v>81</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>228</v>
+        <v>107</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>237</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>476</v>
+        <v>505</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>476</v>
+        <v>505</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>81</v>
@@ -11031,35 +11154,33 @@
         <v>81</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>239</v>
+        <v>111</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>477</v>
+        <v>112</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>478</v>
+        <v>81</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>81</v>
@@ -11095,73 +11216,75 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>244</v>
+        <v>117</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>245</v>
+        <v>107</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J80" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11173,7 +11296,7 @@
         <v>81</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>81</v>
@@ -11209,39 +11332,39 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>253</v>
+        <v>193</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>254</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11261,16 +11384,16 @@
         <v>81</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>257</v>
+        <v>508</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>258</v>
+        <v>509</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11321,7 +11444,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>259</v>
+        <v>507</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11339,21 +11462,21 @@
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>261</v>
+        <v>510</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11373,20 +11496,18 @@
         <v>81</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>263</v>
+        <v>103</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>264</v>
+        <v>104</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -11435,7 +11556,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>267</v>
+        <v>106</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11447,38 +11568,38 @@
         <v>81</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>268</v>
+        <v>107</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
@@ -11490,15 +11611,17 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>483</v>
+        <v>110</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>484</v>
+        <v>111</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -11535,37 +11658,37 @@
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>482</v>
+        <v>117</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>486</v>
+        <v>107</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -11576,10 +11699,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11596,22 +11719,26 @@
         <v>81</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>488</v>
+        <v>220</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
       </c>
@@ -11635,13 +11762,13 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>490</v>
+        <v>225</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>491</v>
+        <v>226</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -11659,7 +11786,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>487</v>
+        <v>227</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11677,21 +11804,21 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>492</v>
+        <v>228</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>493</v>
+        <v>193</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11699,7 +11826,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>89</v>
@@ -11711,19 +11838,23 @@
         <v>81</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>230</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>495</v>
+        <v>231</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
       </c>
@@ -11747,13 +11878,11 @@
         <v>81</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>498</v>
+        <v>235</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -11771,7 +11900,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>494</v>
+        <v>236</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11789,21 +11918,21 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>107</v>
+        <v>228</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>499</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11811,10 +11940,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -11823,35 +11952,35 @@
         <v>81</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>230</v>
+        <v>131</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>501</v>
+        <v>239</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>503</v>
+        <v>241</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>504</v>
+        <v>242</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>81</v>
+        <v>518</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>81</v>
@@ -11863,13 +11992,13 @@
         <v>81</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
@@ -11887,13 +12016,13 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>500</v>
+        <v>244</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
@@ -11905,21 +12034,21 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>507</v>
+        <v>245</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>508</v>
+        <v>246</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11927,10 +12056,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
@@ -11939,18 +12068,20 @@
         <v>81</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>230</v>
+        <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>510</v>
+        <v>248</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -11963,7 +12094,7 @@
         <v>81</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>81</v>
@@ -11975,13 +12106,13 @@
         <v>81</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>513</v>
+        <v>81</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>81</v>
@@ -11999,13 +12130,13 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>509</v>
+        <v>252</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>81</v>
@@ -12017,21 +12148,21 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>514</v>
+        <v>253</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>515</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12042,7 +12173,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
@@ -12051,16 +12182,16 @@
         <v>81</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>517</v>
+        <v>257</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>518</v>
+        <v>258</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12087,13 +12218,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>520</v>
+        <v>81</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -12111,13 +12242,13 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>516</v>
+        <v>259</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>81</v>
@@ -12129,21 +12260,21 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>521</v>
+        <v>260</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>522</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12163,18 +12294,20 @@
         <v>81</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>483</v>
+        <v>263</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>524</v>
+        <v>264</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12223,7 +12356,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>523</v>
+        <v>267</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12241,21 +12374,21 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>526</v>
+        <v>268</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>527</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12278,13 +12411,13 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>230</v>
+        <v>523</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12311,13 +12444,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>531</v>
+        <v>81</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>532</v>
+        <v>81</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12335,7 +12468,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12353,21 +12486,21 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>534</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12378,7 +12511,7 @@
         <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>81</v>
@@ -12390,17 +12523,15 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -12425,13 +12556,13 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>81</v>
+        <v>530</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>81</v>
+        <v>531</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -12449,13 +12580,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>81</v>
@@ -12467,21 +12598,21 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>81</v>
+        <v>533</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12504,13 +12635,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>104</v>
+        <v>535</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>105</v>
+        <v>536</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12537,13 +12668,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>81</v>
+        <v>537</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>81</v>
+        <v>538</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -12561,7 +12692,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>106</v>
+        <v>534</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12573,7 +12704,7 @@
         <v>81</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
@@ -12585,19 +12716,19 @@
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>81</v>
+        <v>539</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12616,18 +12747,20 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>111</v>
+        <v>541</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>112</v>
+        <v>542</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
       </c>
@@ -12651,13 +12784,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>81</v>
+        <v>545</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>81</v>
+        <v>546</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -12675,7 +12808,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>117</v>
+        <v>540</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12687,31 +12820,31 @@
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>107</v>
+        <v>547</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>81</v>
+        <v>548</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12724,26 +12857,22 @@
         <v>81</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>289</v>
+        <v>550</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>81</v>
       </c>
@@ -12767,13 +12896,13 @@
         <v>81</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>81</v>
+        <v>552</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>81</v>
+        <v>553</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>81</v>
@@ -12791,7 +12920,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>291</v>
+        <v>549</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12803,27 +12932,27 @@
         <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>193</v>
+        <v>554</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>81</v>
+        <v>555</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12831,10 +12960,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>81</v>
@@ -12846,13 +12975,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>544</v>
+        <v>230</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12879,13 +13008,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>81</v>
+        <v>559</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>81</v>
+        <v>560</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -12903,13 +13032,13 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>81</v>
@@ -12918,24 +13047,24 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>547</v>
+        <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>390</v>
+        <v>561</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>548</v>
+        <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>549</v>
+        <v>562</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12958,17 +13087,15 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>170</v>
+        <v>523</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -12993,13 +13120,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>554</v>
+        <v>81</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>555</v>
+        <v>81</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13017,7 +13144,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13035,21 +13162,21 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>81</v>
+        <v>567</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13075,14 +13202,12 @@
         <v>230</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -13109,9 +13234,11 @@
       <c r="X97" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y97" s="2"/>
+      <c r="Y97" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13129,7 +13256,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13147,21 +13274,21 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>81</v>
+        <v>573</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>81</v>
+        <v>574</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13172,7 +13299,7 @@
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>81</v>
@@ -13184,15 +13311,17 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -13241,13 +13370,13 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>81</v>
@@ -13259,7 +13388,7 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>383</v>
+        <v>579</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
@@ -13270,10 +13399,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13296,13 +13425,13 @@
         <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>263</v>
+        <v>103</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>566</v>
+        <v>104</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>567</v>
+        <v>105</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13353,7 +13482,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>565</v>
+        <v>106</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13365,38 +13494,38 @@
         <v>81</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>568</v>
+        <v>107</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>81</v>
@@ -13408,16 +13537,16 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>571</v>
+        <v>110</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>572</v>
+        <v>111</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>573</v>
+        <v>112</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>574</v>
+        <v>113</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13467,30 +13596,822 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>570</v>
+        <v>117</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ100" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK100" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN100" t="s" s="2">
+      <c r="AK102" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Y104" s="2"/>
+      <c r="Z104" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T12:23:37+00:00</t>
+    <t>2026-10-13T09:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -949,7 +949,7 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActEncounterCode-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActEncounterCode-cisis|20260916095454</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T09:01:17+00:00</t>
+    <t>2026-10-13T11:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
